--- a/paper/tables/data_real_correlations_per_dataset_cvi_to_ari.xlsx
+++ b/paper/tables/data_real_correlations_per_dataset_cvi_to_ari.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\Clustering-Validity\paper\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{FB502B0A-695B-4F2D-B498-8655EF3BCE10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC7E543D-6DE0-4CCA-935C-0F314C70EF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{27DB1044-5758-4C17-8EA7-BA8951B601EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{27DB1044-5758-4C17-8EA7-BA8951B601EE}"/>
   </bookViews>
   <sheets>
     <sheet name="data_real_correlations_per_data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>ecoli</t>
   </si>
@@ -140,6 +153,12 @@
   </si>
   <si>
     <t>AD-idea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correct </t>
+  </si>
+  <si>
+    <t>Errors</t>
   </si>
 </sst>
 </file>
@@ -147,7 +166,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -626,11 +645,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1006,10 +1024,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEF81A6C-9417-4EDF-BB93-5D60E8C7C494}">
-  <dimension ref="A1:I33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +1052,14 @@
       <c r="I1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1063,8 +1087,14 @@
       <c r="I2" s="1">
         <v>-0.59107557172682101</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J2">
+        <v>8</v>
+      </c>
+      <c r="K2">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1092,8 +1122,14 @@
       <c r="I3" s="1">
         <v>-0.59951939873080395</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1121,8 +1157,14 @@
       <c r="I4" s="1">
         <v>0.46636050112048</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -1150,8 +1192,14 @@
       <c r="I5" s="1">
         <v>0.61848145936769106</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -1179,8 +1227,14 @@
       <c r="I6" s="1">
         <v>-0.58712180409348502</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J6">
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1208,8 +1262,14 @@
       <c r="I7" s="2">
         <v>0.89495734338872601</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J7">
+        <v>8</v>
+      </c>
+      <c r="K7">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1237,8 +1297,14 @@
       <c r="I8" s="1">
         <v>-0.288564261413498</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J8">
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1266,8 +1332,14 @@
       <c r="I9" s="1">
         <v>0.79813233760205704</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J9">
+        <v>9</v>
+      </c>
+      <c r="K9">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -1295,8 +1367,14 @@
       <c r="I10" s="1">
         <v>-0.270831747151216</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -1324,8 +1402,14 @@
       <c r="I11" s="1">
         <v>-9.0800639309226203E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J11">
+        <v>9</v>
+      </c>
+      <c r="K11">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1353,8 +1437,14 @@
       <c r="I12" s="1">
         <v>-8.9766832761710696E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J12">
+        <v>7</v>
+      </c>
+      <c r="K12">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1382,8 +1472,14 @@
       <c r="I13" s="1">
         <v>0.35630570174107301</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J13">
+        <v>9</v>
+      </c>
+      <c r="K13">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1411,8 +1507,14 @@
       <c r="I14" s="1">
         <v>-0.56965249936977702</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J14">
+        <v>5</v>
+      </c>
+      <c r="K14">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1440,8 +1542,14 @@
       <c r="I15" s="1">
         <v>-0.477259157446774</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J15">
+        <v>4</v>
+      </c>
+      <c r="K15">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1577,14 @@
       <c r="I16" s="1">
         <v>-0.71728333554184698</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16">
+        <v>6</v>
+      </c>
+      <c r="K16">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1498,8 +1612,14 @@
       <c r="I17" s="1">
         <v>-1.95620035933383E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17">
+        <v>7</v>
+      </c>
+      <c r="K17">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -1527,8 +1647,14 @@
       <c r="I18" s="1">
         <v>-0.248604009525974</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18">
+        <v>8</v>
+      </c>
+      <c r="K18">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1556,8 +1682,14 @@
       <c r="I19" s="1">
         <v>0.24881126395924499</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19">
+        <v>13</v>
+      </c>
+      <c r="K19">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -1585,8 +1717,14 @@
       <c r="I20" s="1">
         <v>0.11725567914348101</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20">
+        <v>11</v>
+      </c>
+      <c r="K20">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -1614,8 +1752,14 @@
       <c r="I21" s="1">
         <v>0.43987783834123001</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21">
+        <v>9</v>
+      </c>
+      <c r="K21">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -1643,8 +1787,14 @@
       <c r="I22" s="1">
         <v>-0.45785452383825298</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J22">
+        <v>11</v>
+      </c>
+      <c r="K22">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1672,8 +1822,14 @@
       <c r="I23" s="1">
         <v>-0.57114573007914304</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J23">
+        <v>7</v>
+      </c>
+      <c r="K23">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -1701,8 +1857,14 @@
       <c r="I24" s="1">
         <v>-0.216071490702403</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>10</v>
+      </c>
+      <c r="K24">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -1730,8 +1892,14 @@
       <c r="I25" s="1">
         <v>-0.165303015306864</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J25">
+        <v>8</v>
+      </c>
+      <c r="K25">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>32</v>
       </c>
@@ -1759,8 +1927,14 @@
       <c r="I26" s="1">
         <v>-0.32272118049793902</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J26">
+        <v>7</v>
+      </c>
+      <c r="K26">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -1788,8 +1962,14 @@
       <c r="I27" s="1">
         <v>-0.231801044244551</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J27">
+        <v>9</v>
+      </c>
+      <c r="K27">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -1817,12 +1997,18 @@
       <c r="I28" s="1">
         <v>-0.28128902684491702</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J28">
+        <v>8</v>
+      </c>
+      <c r="K28">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="1">
         <v>0.52908656922324304</v>
       </c>
       <c r="C29" s="1">
@@ -1840,14 +2026,20 @@
       <c r="G29" s="1">
         <v>0.86154138616190601</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="1">
         <v>0.68939006387466395</v>
       </c>
       <c r="I29" s="1">
         <v>0.89327474232566095</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J29">
+        <v>11</v>
+      </c>
+      <c r="K29">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>36</v>
       </c>
@@ -1875,8 +2067,14 @@
       <c r="I30" s="1">
         <v>-0.66338474020794003</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J30">
+        <v>9</v>
+      </c>
+      <c r="K30">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>37</v>
       </c>
@@ -1904,8 +2102,14 @@
       <c r="I31" s="1">
         <v>-0.42768906297077403</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J31">
+        <v>9</v>
+      </c>
+      <c r="K31">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1933,8 +2137,14 @@
       <c r="I32" s="1">
         <v>0.56389501885133098</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J32">
+        <v>10</v>
+      </c>
+      <c r="K32">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -1961,6 +2171,12 @@
       </c>
       <c r="I33" s="1">
         <v>-0.114814340484723</v>
+      </c>
+      <c r="J33">
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <v>843</v>
       </c>
     </row>
   </sheetData>
